--- a/database.xlsx
+++ b/database.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/766bdf64b321323f/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CAF40AB-3853-46AE-9CC0-A89FBE1B783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2C2012-C4D7-48B1-8603-4F40EAAA9C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C4B59B0E-D649-4F64-97DA-F4C0E3FEC917}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
   <si>
     <t>Integrante</t>
   </si>
@@ -77,13 +77,7 @@
     <t>Red_Maluco</t>
   </si>
   <si>
-    <t>Xitbutguer</t>
-  </si>
-  <si>
     <t>Jay jay leva jatinho</t>
-  </si>
-  <si>
-    <t>Xitbuerguer</t>
   </si>
 </sst>
 </file>
@@ -781,7 +775,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -873,7 +867,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>14</v>
@@ -942,7 +936,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>5</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2C2012-C4D7-48B1-8603-4F40EAAA9C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BBBFE-F3E6-4FDA-B861-BAC047976887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C4B59B0E-D649-4F64-97DA-F4C0E3FEC917}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
   <si>
     <t>Integrante</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Jay jay leva jatinho</t>
+  </si>
+  <si>
+    <t>Velhucho</t>
   </si>
 </sst>
 </file>
@@ -133,8 +136,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}" name="Tabela1" displayName="Tabela1" ref="A1:G21" totalsRowShown="0">
-  <autoFilter ref="A1:G21" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}" name="Tabela1" displayName="Tabela1" ref="A1:G23" totalsRowShown="0">
+  <autoFilter ref="A1:G23" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{2B9CEDFD-8555-4F2E-B50C-284FFE26AA68}" name="Integrante"/>
     <tableColumn id="2" xr3:uid="{31CF14F7-9D54-413A-A961-4646B1D57D2C}" name="Kills"/>
@@ -465,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5017A357-EABB-46F0-B6F4-2CF186408F4E}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -867,45 +870,45 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -913,22 +916,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -936,24 +939,70 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <v>14</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>30</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>27</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>10</v>
       </c>
-      <c r="B21">
-        <v>5</v>
-      </c>
-      <c r="C21">
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
         <v>15</v>
       </c>
-      <c r="D21">
+      <c r="D23">
         <v>4</v>
       </c>
-      <c r="E21">
+      <c r="E23">
         <v>0</v>
       </c>
-      <c r="F21">
+      <c r="F23">
         <v>13</v>
       </c>
-      <c r="G21">
+      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0BBBFE-F3E6-4FDA-B861-BAC047976887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB3E1CD-EE59-474C-B03D-536A0D41B036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C4B59B0E-D649-4F64-97DA-F4C0E3FEC917}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{C4B59B0E-D649-4F64-97DA-F4C0E3FEC917}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
   <si>
     <t>Integrante</t>
   </si>
@@ -136,8 +136,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}" name="Tabela1" displayName="Tabela1" ref="A1:G23" totalsRowShown="0">
-  <autoFilter ref="A1:G23" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}" name="Tabela1" displayName="Tabela1" ref="A1:G30" totalsRowShown="0">
+  <autoFilter ref="A1:G30" xr:uid="{910F6181-1C5D-458A-8F8D-2A0B204C9817}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{2B9CEDFD-8555-4F2E-B50C-284FFE26AA68}" name="Integrante"/>
     <tableColumn id="2" xr3:uid="{31CF14F7-9D54-413A-A961-4646B1D57D2C}" name="Kills"/>
@@ -468,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5017A357-EABB-46F0-B6F4-2CF186408F4E}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -1006,6 +1006,167 @@
         <v>5</v>
       </c>
     </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>52</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>16</v>
+      </c>
+      <c r="C25">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>40</v>
+      </c>
+      <c r="G25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26">
+        <v>15</v>
+      </c>
+      <c r="C26">
+        <v>18</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>36</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>30</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28">
+        <v>19</v>
+      </c>
+      <c r="C28">
+        <v>16</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>28</v>
+      </c>
+      <c r="G28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29">
+        <v>15</v>
+      </c>
+      <c r="C29">
+        <v>17</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>19</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>22</v>
+      </c>
+      <c r="G30">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
